--- a/docs/inputs/slope/xslope_rface.xlsx
+++ b/docs/inputs/slope/xslope_rface.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF14F856-A563-434E-91CD-184FA2D5B1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252F6D64-D8D9-5346-99D4-CC3885A4756E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5900" yWindow="4020" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="22000" yWindow="2420" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1050,19 +1050,22 @@
     <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1083,18 +1086,29 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8026,11 +8040,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -8549,34 +8563,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="E2" s="48" t="s">
+      <c r="C2" s="53"/>
+      <c r="E2" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="48"/>
-      <c r="H2" s="48" t="s">
+      <c r="F2" s="49"/>
+      <c r="H2" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="K2" s="48" t="s">
+      <c r="I2" s="49"/>
+      <c r="K2" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="N2" s="48" t="s">
+      <c r="L2" s="49"/>
+      <c r="N2" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="Q2" s="48" t="s">
+      <c r="O2" s="49"/>
+      <c r="Q2" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="R2" s="48"/>
+      <c r="R2" s="49"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
       <c r="E3" s="37" t="s">
         <v>97</v>
       </c>
@@ -8965,34 +8979,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="E2" s="49" t="s">
+      <c r="C2" s="54"/>
+      <c r="E2" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="F2" s="49"/>
-      <c r="H2" s="49" t="s">
+      <c r="F2" s="50"/>
+      <c r="H2" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="I2" s="49"/>
-      <c r="K2" s="49" t="s">
+      <c r="I2" s="50"/>
+      <c r="K2" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="L2" s="49"/>
-      <c r="N2" s="49" t="s">
+      <c r="L2" s="50"/>
+      <c r="N2" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="Q2" s="49" t="s">
+      <c r="O2" s="50"/>
+      <c r="Q2" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="R2" s="49"/>
+      <c r="R2" s="50"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="E3" s="39" t="s">
         <v>97</v>
       </c>
@@ -9430,36 +9444,36 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="44" t="s">
+      <c r="L7" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44" t="s">
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44" t="s">
+      <c r="S7" s="45"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="X7" s="44"/>
+      <c r="X7" s="45"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -10267,38 +10281,33 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E12:F50">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>$D12="cp"</formula>
+  <conditionalFormatting sqref="E9:F50">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N50">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="2" priority="14">
+    <cfRule type="expression" dxfId="4" priority="14">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="1" priority="9">
-      <formula>$D9="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9:F11">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="9">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10355,74 +10364,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="46"/>
+      <c r="D4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="G4" s="47" t="s">
+      <c r="E4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="J4" s="47" t="s">
+      <c r="H4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="M4" s="47" t="s">
+      <c r="K4" s="46"/>
+      <c r="M4" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="47"/>
-      <c r="P4" s="47" t="s">
+      <c r="N4" s="46"/>
+      <c r="P4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="47"/>
+      <c r="Q4" s="46"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="47" t="s">
+      <c r="S4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="47"/>
+      <c r="T4" s="46"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="47" t="s">
+      <c r="V4" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="47"/>
+      <c r="W4" s="46"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="47" t="s">
+      <c r="Y4" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="47"/>
+      <c r="Z4" s="46"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="47" t="s">
+      <c r="AB4" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="47"/>
-      <c r="AE4" s="47" t="s">
+      <c r="AC4" s="46"/>
+      <c r="AE4" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="47"/>
+      <c r="AF4" s="46"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="47" t="s">
+      <c r="AH4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="47"/>
+      <c r="AI4" s="46"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="47" t="s">
+      <c r="AK4" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="47"/>
+      <c r="AL4" s="46"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="47" t="s">
+      <c r="AN4" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="47"/>
+      <c r="AO4" s="46"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="47" t="s">
+      <c r="AQ4" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="47"/>
+      <c r="AR4" s="46"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10525,89 +10534,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="45" t="str">
+      <c r="A6" s="47" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Silt</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="D6" s="45" t="str">
+      <c r="B6" s="48"/>
+      <c r="D6" s="47" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Sand</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="G6" s="45" t="str">
+      <c r="E6" s="48"/>
+      <c r="G6" s="47" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Clay</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="J6" s="45" t="str">
+      <c r="H6" s="48"/>
+      <c r="J6" s="47" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="46"/>
-      <c r="M6" s="45" t="str">
+      <c r="K6" s="48"/>
+      <c r="M6" s="47" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="46"/>
-      <c r="P6" s="45" t="str">
+      <c r="N6" s="48"/>
+      <c r="P6" s="47" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="46"/>
+      <c r="Q6" s="48"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="45" t="str">
+      <c r="S6" s="47" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="46"/>
+      <c r="T6" s="48"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="45" t="str">
+      <c r="V6" s="47" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="46"/>
+      <c r="W6" s="48"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="45" t="str">
+      <c r="Y6" s="47" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="46"/>
+      <c r="Z6" s="48"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="45" t="str">
+      <c r="AB6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="46"/>
-      <c r="AE6" s="45" t="str">
+      <c r="AC6" s="48"/>
+      <c r="AE6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="46"/>
+      <c r="AF6" s="48"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="45" t="str">
+      <c r="AH6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="46"/>
+      <c r="AI6" s="48"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="45" t="str">
+      <c r="AK6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="46"/>
+      <c r="AL6" s="48"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="45" t="str">
+      <c r="AN6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="46"/>
+      <c r="AO6" s="48"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="45" t="str">
+      <c r="AQ6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="46"/>
+      <c r="AR6" s="48"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -10716,14 +10725,14 @@
       <c r="B8" s="17">
         <v>84</v>
       </c>
-      <c r="C8" s="54"/>
+      <c r="C8" s="43"/>
       <c r="D8" s="16">
         <v>0</v>
       </c>
       <c r="E8" s="17">
         <v>64</v>
       </c>
-      <c r="F8" s="54"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="16">
         <v>0</v>
       </c>
@@ -10770,14 +10779,14 @@
       <c r="B9" s="19">
         <v>84</v>
       </c>
-      <c r="C9" s="54"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="18">
         <v>174.7</v>
       </c>
       <c r="E9" s="19">
         <v>64</v>
       </c>
-      <c r="F9" s="54"/>
+      <c r="F9" s="43"/>
       <c r="G9" s="18">
         <v>320</v>
       </c>
@@ -10824,14 +10833,14 @@
       <c r="B10" s="19">
         <v>64</v>
       </c>
-      <c r="C10" s="54"/>
+      <c r="C10" s="43"/>
       <c r="D10" s="18">
         <v>204.3</v>
       </c>
       <c r="E10" s="19">
         <v>40</v>
       </c>
-      <c r="F10" s="54"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="18"/>
       <c r="H10" s="19"/>
       <c r="J10" s="3"/>
@@ -11549,36 +11558,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11594,14 +11603,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="D2" s="49" t="s">
+      <c r="B2" s="49"/>
+      <c r="D2" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="49"/>
+      <c r="E2" s="50"/>
       <c r="G2" s="24" t="s">
         <v>85</v>
       </c>
@@ -11984,12 +11993,24 @@
       <c r="N16" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D12" xr:uid="{06E9E004-FC39-FE49-926A-912F810F5089}">
+  <conditionalFormatting sqref="E3:E42">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>OR($D3="Intercept", $D3="Radius")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:G42">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>OR($D3="Depth",$D3="Radius")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H42">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>OR($D3="Depth",$D3="Intercept")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D52" xr:uid="{5A662065-905E-B648-88D3-0AA0500DD384}">
       <formula1>$J$3:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4" xr:uid="{0D88F71E-BAB5-8144-B1E2-0FEC761973B3}">
-      <formula1>$J$5:$J$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12176,36 +12197,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="F2" s="50" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="F2" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="J2" s="50" t="s">
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="J2" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="N2" s="50" t="s">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="N2" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="R2" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="V2" s="50" t="s">
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="V2" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -12676,36 +12697,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="F2" s="51" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="F2" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="J2" s="51" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="N2" s="51" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="N2" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="R2" s="51" t="s">
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="R2" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="V2" s="51" t="s">
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="V2" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">

--- a/docs/inputs/slope/xslope_rface.xlsx
+++ b/docs/inputs/slope/xslope_rface.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252F6D64-D8D9-5346-99D4-CC3885A4756E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A28624-35E5-7641-99BA-1C13F49C4AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22000" yWindow="2420" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="7240" yWindow="3340" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1059,13 +1059,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10364,74 +10364,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="D4" s="46" t="s">
+      <c r="B4" s="48"/>
+      <c r="D4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="E4" s="48"/>
+      <c r="G4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="J4" s="46" t="s">
+      <c r="H4" s="48"/>
+      <c r="J4" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="46"/>
-      <c r="M4" s="46" t="s">
+      <c r="K4" s="48"/>
+      <c r="M4" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="46"/>
-      <c r="P4" s="46" t="s">
+      <c r="N4" s="48"/>
+      <c r="P4" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="46"/>
+      <c r="Q4" s="48"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="46" t="s">
+      <c r="S4" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="46"/>
+      <c r="T4" s="48"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="46" t="s">
+      <c r="V4" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="46"/>
+      <c r="W4" s="48"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="46" t="s">
+      <c r="Y4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="46"/>
+      <c r="Z4" s="48"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="46" t="s">
+      <c r="AB4" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="46"/>
-      <c r="AE4" s="46" t="s">
+      <c r="AC4" s="48"/>
+      <c r="AE4" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="46"/>
+      <c r="AF4" s="48"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="46" t="s">
+      <c r="AH4" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="46"/>
+      <c r="AI4" s="48"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="46" t="s">
+      <c r="AK4" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="46"/>
+      <c r="AL4" s="48"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="46" t="s">
+      <c r="AN4" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="46"/>
+      <c r="AO4" s="48"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="46" t="s">
+      <c r="AQ4" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="46"/>
+      <c r="AR4" s="48"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10534,89 +10534,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="str">
+      <c r="A6" s="46" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Silt</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="D6" s="47" t="str">
+      <c r="B6" s="47"/>
+      <c r="D6" s="46" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Sand</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="G6" s="47" t="str">
+      <c r="E6" s="47"/>
+      <c r="G6" s="46" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Clay</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="J6" s="47" t="str">
+      <c r="H6" s="47"/>
+      <c r="J6" s="46" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="48"/>
-      <c r="M6" s="47" t="str">
+      <c r="K6" s="47"/>
+      <c r="M6" s="46" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="48"/>
-      <c r="P6" s="47" t="str">
+      <c r="N6" s="47"/>
+      <c r="P6" s="46" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="48"/>
+      <c r="Q6" s="47"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="47" t="str">
+      <c r="S6" s="46" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="48"/>
+      <c r="T6" s="47"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="47" t="str">
+      <c r="V6" s="46" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="48"/>
+      <c r="W6" s="47"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="47" t="str">
+      <c r="Y6" s="46" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="48"/>
+      <c r="Z6" s="47"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="47" t="str">
+      <c r="AB6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="48"/>
-      <c r="AE6" s="47" t="str">
+      <c r="AC6" s="47"/>
+      <c r="AE6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="48"/>
+      <c r="AF6" s="47"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="47" t="str">
+      <c r="AH6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="48"/>
+      <c r="AI6" s="47"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="47" t="str">
+      <c r="AK6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="48"/>
+      <c r="AL6" s="47"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="47" t="str">
+      <c r="AN6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="48"/>
+      <c r="AO6" s="47"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="47" t="str">
+      <c r="AQ6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="48"/>
+      <c r="AR6" s="47"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11558,36 +11558,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/inputs/slope/xslope_rface.xlsx
+++ b/docs/inputs/slope/xslope_rface.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A28624-35E5-7641-99BA-1C13F49C4AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EC81B6-AD75-8348-9E59-67F676A02D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7240" yWindow="3340" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
@@ -934,7 +934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1059,13 +1059,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1085,6 +1085,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9584,8 +9587,12 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="W9" s="55">
+        <v>700000</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
@@ -9622,8 +9629,12 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="W10" s="55">
+        <v>700000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
@@ -9660,8 +9671,12 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="W11" s="55">
+        <v>700000</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
@@ -10364,74 +10379,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="D4" s="48" t="s">
+      <c r="B4" s="46"/>
+      <c r="D4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="G4" s="48" t="s">
+      <c r="E4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="J4" s="48" t="s">
+      <c r="H4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="M4" s="48" t="s">
+      <c r="K4" s="46"/>
+      <c r="M4" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="P4" s="48" t="s">
+      <c r="N4" s="46"/>
+      <c r="P4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="48"/>
+      <c r="Q4" s="46"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="48"/>
+      <c r="T4" s="46"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="48"/>
+      <c r="W4" s="46"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="48" t="s">
+      <c r="Y4" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="48"/>
+      <c r="Z4" s="46"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="48" t="s">
+      <c r="AB4" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="48"/>
-      <c r="AE4" s="48" t="s">
+      <c r="AC4" s="46"/>
+      <c r="AE4" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="48"/>
+      <c r="AF4" s="46"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="48"/>
+      <c r="AI4" s="46"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="48"/>
+      <c r="AL4" s="46"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="48"/>
+      <c r="AO4" s="46"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="48"/>
+      <c r="AR4" s="46"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10534,89 +10549,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="str">
+      <c r="A6" s="47" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Silt</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="D6" s="46" t="str">
+      <c r="B6" s="48"/>
+      <c r="D6" s="47" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Sand</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="G6" s="46" t="str">
+      <c r="E6" s="48"/>
+      <c r="G6" s="47" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>Clay</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="J6" s="46" t="str">
+      <c r="H6" s="48"/>
+      <c r="J6" s="47" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="47"/>
-      <c r="M6" s="46" t="str">
+      <c r="K6" s="48"/>
+      <c r="M6" s="47" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="47"/>
-      <c r="P6" s="46" t="str">
+      <c r="N6" s="48"/>
+      <c r="P6" s="47" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="48"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="46" t="str">
+      <c r="S6" s="47" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="48"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="46" t="str">
+      <c r="V6" s="47" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="47"/>
+      <c r="W6" s="48"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="46" t="str">
+      <c r="Y6" s="47" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="47"/>
+      <c r="Z6" s="48"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="46" t="str">
+      <c r="AB6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="47"/>
-      <c r="AE6" s="46" t="str">
+      <c r="AC6" s="48"/>
+      <c r="AE6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="47"/>
+      <c r="AF6" s="48"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="46" t="str">
+      <c r="AH6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="47"/>
+      <c r="AI6" s="48"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="46" t="str">
+      <c r="AK6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="47"/>
+      <c r="AL6" s="48"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="46" t="str">
+      <c r="AN6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="47"/>
+      <c r="AO6" s="48"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="46" t="str">
+      <c r="AQ6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="47"/>
+      <c r="AR6" s="48"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11558,36 +11573,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/inputs/slope/xslope_rface.xlsx
+++ b/docs/inputs/slope/xslope_rface.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>X</t>
   </si>
@@ -630,6 +630,37 @@
   </si>
   <si>
     <t>Clay</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8039,7 +8070,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9506,8 +9537,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9528,7 +9559,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10296,7 +10327,7 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="8" priority="1">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10311,7 +10342,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="5" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>

--- a/docs/inputs/slope/xslope_rface.xlsx
+++ b/docs/inputs/slope/xslope_rface.xlsx
@@ -5899,7 +5899,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>700000.0</v>
       </c>
@@ -6023,7 +6025,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>700000.0</v>
       </c>
@@ -6147,7 +6151,9 @@
       <c r="K13" s="3">
         <v>0.0</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M13" s="3">
         <v>700000.0</v>
       </c>
